--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>130177125</v>
       </c>
       <c r="B4" t="n">
-        <v>91876</v>
+        <v>91878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130177159</v>
       </c>
       <c r="B5" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>130177134</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130177154</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>130177137</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>130177153</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>130177150</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>130177149</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>130177143</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130177129</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177125</v>
+        <v>130177134</v>
       </c>
       <c r="B4" t="n">
-        <v>91878</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604794</v>
+        <v>604780</v>
       </c>
       <c r="R4" t="n">
-        <v>6675010</v>
+        <v>6675057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177159</v>
+        <v>130177125</v>
       </c>
       <c r="B5" t="n">
-        <v>91661</v>
+        <v>91965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,19 +1001,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604851</v>
+        <v>604794</v>
       </c>
       <c r="R5" t="n">
-        <v>6674989</v>
+        <v>6675010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177134</v>
+        <v>130177154</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1115,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604780</v>
+        <v>604852</v>
       </c>
       <c r="R6" t="n">
-        <v>6675057</v>
+        <v>6674964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,34 +1184,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177154</v>
+        <v>130177159</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604852</v>
+        <v>604851</v>
       </c>
       <c r="R7" t="n">
-        <v>6674964</v>
+        <v>6674989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>130177128</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>130177137</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>130177153</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>130177150</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>130177149</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>130177143</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177159</v>
+        <v>130177125</v>
       </c>
       <c r="B4" t="n">
-        <v>91748</v>
+        <v>91968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,19 +900,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -920,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604851</v>
+        <v>604794</v>
       </c>
       <c r="R4" t="n">
-        <v>6674989</v>
+        <v>6675010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177125</v>
+        <v>130177159</v>
       </c>
       <c r="B5" t="n">
-        <v>91965</v>
+        <v>91751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,23 +997,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1101</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604794</v>
+        <v>604851</v>
       </c>
       <c r="R5" t="n">
-        <v>6675010</v>
+        <v>6674989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>130177134</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130177154</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>130177137</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>130177153</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>130177150</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>130177149</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>130177143</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130177129</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130177125</v>
       </c>
       <c r="B4" t="n">
-        <v>91968</v>
+        <v>91994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130177159</v>
       </c>
       <c r="B5" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>130177134</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130177154</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>130177128</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>130177137</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>130177153</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>130177150</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>130177149</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>130177143</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177125</v>
+        <v>130177159</v>
       </c>
       <c r="B4" t="n">
-        <v>91994</v>
+        <v>91778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,23 +900,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -924,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604794</v>
+        <v>604851</v>
       </c>
       <c r="R4" t="n">
-        <v>6675010</v>
+        <v>6674989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,30 +982,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177159</v>
+        <v>130177154</v>
       </c>
       <c r="B5" t="n">
-        <v>91777</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604851</v>
+        <v>604852</v>
       </c>
       <c r="R5" t="n">
-        <v>6674989</v>
+        <v>6674964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>130177134</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177154</v>
+        <v>130177125</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604852</v>
+        <v>604794</v>
       </c>
       <c r="R7" t="n">
-        <v>6674964</v>
+        <v>6675010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>130177137</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>130177153</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>130177150</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>130177149</v>
       </c>
       <c r="B19" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>130177143</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177159</v>
+        <v>130177125</v>
       </c>
       <c r="B4" t="n">
-        <v>91778</v>
+        <v>91996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,19 +900,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -920,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604851</v>
+        <v>604794</v>
       </c>
       <c r="R4" t="n">
-        <v>6674989</v>
+        <v>6675010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177154</v>
+        <v>130177134</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,17 +1014,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604852</v>
+        <v>604780</v>
       </c>
       <c r="R5" t="n">
-        <v>6674964</v>
+        <v>6675057</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177134</v>
+        <v>130177154</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1115,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604780</v>
+        <v>604852</v>
       </c>
       <c r="R6" t="n">
-        <v>6675057</v>
+        <v>6674964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177125</v>
+        <v>130177159</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1195,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1101</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604794</v>
+        <v>604851</v>
       </c>
       <c r="R7" t="n">
-        <v>6675010</v>
+        <v>6674989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130177137</v>
+        <v>130177153</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,21 +1811,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604812</v>
+        <v>604865</v>
       </c>
       <c r="R13" t="n">
-        <v>6675044</v>
+        <v>6674998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,10 +1880,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130177153</v>
+        <v>130177137</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,17 +1908,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604865</v>
+        <v>604812</v>
       </c>
       <c r="R14" t="n">
-        <v>6674998</v>
+        <v>6675044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130177150</v>
+        <v>130177143</v>
       </c>
       <c r="B18" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604792</v>
+        <v>604805</v>
       </c>
       <c r="R18" t="n">
-        <v>6675040</v>
+        <v>6674997</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130177149</v>
+        <v>130177150</v>
       </c>
       <c r="B19" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604741</v>
+        <v>604792</v>
       </c>
       <c r="R19" t="n">
-        <v>6675095</v>
+        <v>6675040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130177143</v>
+        <v>130177149</v>
       </c>
       <c r="B20" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604805</v>
+        <v>604741</v>
       </c>
       <c r="R20" t="n">
-        <v>6674997</v>
+        <v>6675095</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130177129</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177125</v>
+        <v>130177134</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604794</v>
+        <v>604780</v>
       </c>
       <c r="R4" t="n">
-        <v>6675010</v>
+        <v>6675057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177134</v>
+        <v>130177154</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +1018,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604780</v>
+        <v>604852</v>
       </c>
       <c r="R5" t="n">
-        <v>6675057</v>
+        <v>6674964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,34 +1087,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177154</v>
+        <v>130177159</v>
       </c>
       <c r="B6" t="n">
-        <v>98951</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1122,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604852</v>
+        <v>604851</v>
       </c>
       <c r="R6" t="n">
-        <v>6674964</v>
+        <v>6674989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177159</v>
+        <v>130177125</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>91998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,19 +1191,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604851</v>
+        <v>604794</v>
       </c>
       <c r="R7" t="n">
-        <v>6674989</v>
+        <v>6675010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>130177128</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130177135</v>
       </c>
       <c r="B11" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>130177151</v>
       </c>
       <c r="B12" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130177153</v>
+        <v>130177137</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,17 +1811,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604865</v>
+        <v>604812</v>
       </c>
       <c r="R13" t="n">
-        <v>6674998</v>
+        <v>6675044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130177137</v>
+        <v>130177153</v>
       </c>
       <c r="B14" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1912,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604812</v>
+        <v>604865</v>
       </c>
       <c r="R14" t="n">
-        <v>6675044</v>
+        <v>6674998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130177158</v>
       </c>
       <c r="B16" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>130177146</v>
       </c>
       <c r="B17" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130177143</v>
+        <v>130177150</v>
       </c>
       <c r="B18" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604805</v>
+        <v>604792</v>
       </c>
       <c r="R18" t="n">
-        <v>6674997</v>
+        <v>6675040</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130177150</v>
+        <v>130177149</v>
       </c>
       <c r="B19" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604792</v>
+        <v>604741</v>
       </c>
       <c r="R19" t="n">
-        <v>6675040</v>
+        <v>6675095</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130177149</v>
+        <v>130177143</v>
       </c>
       <c r="B20" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604741</v>
+        <v>604805</v>
       </c>
       <c r="R20" t="n">
-        <v>6675095</v>
+        <v>6674997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
         <v>130177145</v>
       </c>
       <c r="B21" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130177155</v>
       </c>
       <c r="B23" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -2877,7 +2877,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130382901</v>
       </c>
       <c r="B25" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117171933</v>
+        <v>130177125</v>
       </c>
       <c r="B2" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordansjö naturreservat (Nordansjö naturreservat), Upl</t>
+          <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604837</v>
+        <v>604794</v>
       </c>
       <c r="R2" t="n">
-        <v>6674989</v>
+        <v>6675010</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,26 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130177129</v>
+        <v>130177128</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604750</v>
+        <v>604813</v>
       </c>
       <c r="R3" t="n">
-        <v>6675096</v>
+        <v>6674927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spår, "flervåningshus" i gran</t>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177134</v>
+        <v>130177129</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604780</v>
+        <v>604750</v>
       </c>
       <c r="R4" t="n">
-        <v>6675057</v>
+        <v>6675096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spår, "flervåningshus" i gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177154</v>
+        <v>117171933</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,17 +1007,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Intill Nordansjö naturreservat, Upl</t>
+          <t>Nordansjö naturreservat, Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604852</v>
+        <v>604837</v>
       </c>
       <c r="R5" t="n">
-        <v>6674964</v>
+        <v>6674989</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1041,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,53 +1071,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177159</v>
+        <v>130177134</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604851</v>
+        <v>604780</v>
       </c>
       <c r="R6" t="n">
-        <v>6674989</v>
+        <v>6675057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,45 +1184,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177125</v>
+        <v>130177135</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604794</v>
+        <v>604779</v>
       </c>
       <c r="R7" t="n">
-        <v>6675010</v>
+        <v>6675050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1288,7 @@
         <v>130177136</v>
       </c>
       <c r="B8" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,45 +1386,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130177128</v>
+        <v>130177137</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604813</v>
+        <v>604812</v>
       </c>
       <c r="R9" t="n">
-        <v>6674927</v>
+        <v>6675044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,11 +1461,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,7 +1490,7 @@
         <v>130177138</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130177135</v>
+        <v>130177141</v>
       </c>
       <c r="B11" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1611,7 +1618,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1620,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604779</v>
+        <v>604880</v>
       </c>
       <c r="R11" t="n">
-        <v>6675050</v>
+        <v>6675034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130177151</v>
+        <v>130177143</v>
       </c>
       <c r="B12" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,7 +1719,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1721,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604783</v>
+        <v>604805</v>
       </c>
       <c r="R12" t="n">
-        <v>6674916</v>
+        <v>6674997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130177137</v>
+        <v>130177145</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,7 +1820,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1822,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604812</v>
+        <v>604806</v>
       </c>
       <c r="R13" t="n">
-        <v>6675044</v>
+        <v>6674935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130177153</v>
+        <v>130177146</v>
       </c>
       <c r="B14" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,17 +1919,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604865</v>
+        <v>604869</v>
       </c>
       <c r="R14" t="n">
-        <v>6674998</v>
+        <v>6675008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1995,7 @@
         <v>130177148</v>
       </c>
       <c r="B15" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,41 +2093,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130177158</v>
+        <v>130177149</v>
       </c>
       <c r="B16" t="n">
-        <v>91781</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604848</v>
+        <v>604741</v>
       </c>
       <c r="R16" t="n">
-        <v>6674988</v>
+        <v>6675095</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130177146</v>
+        <v>130177150</v>
       </c>
       <c r="B17" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,7 +2224,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2214,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604869</v>
+        <v>604792</v>
       </c>
       <c r="R17" t="n">
-        <v>6675008</v>
+        <v>6675040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,10 +2295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130177150</v>
+        <v>130177151</v>
       </c>
       <c r="B18" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,7 +2325,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2315,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604792</v>
+        <v>604783</v>
       </c>
       <c r="R18" t="n">
-        <v>6675040</v>
+        <v>6674916</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130177149</v>
+        <v>130177153</v>
       </c>
       <c r="B19" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,21 +2424,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604741</v>
+        <v>604865</v>
       </c>
       <c r="R19" t="n">
-        <v>6675095</v>
+        <v>6674998</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2478,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130177143</v>
+        <v>130177154</v>
       </c>
       <c r="B20" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,21 +2521,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604805</v>
+        <v>604852</v>
       </c>
       <c r="R20" t="n">
-        <v>6674997</v>
+        <v>6674964</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2579,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130177145</v>
+        <v>130177155</v>
       </c>
       <c r="B21" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,21 +2618,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>604806</v>
+        <v>604783</v>
       </c>
       <c r="R21" t="n">
-        <v>6674935</v>
+        <v>6674860</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2690,7 @@
         <v>130177157</v>
       </c>
       <c r="B22" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,10 +2784,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130177155</v>
+        <v>130382901</v>
       </c>
       <c r="B23" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2806,16 +2813,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Intill Nordansjö naturreservat, Upl</t>
+          <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604783</v>
+        <v>604824</v>
       </c>
       <c r="R23" t="n">
-        <v>6674860</v>
+        <v>6674944</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,12 +2854,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,7 +2889,7 @@
         <v>130382902</v>
       </c>
       <c r="B24" t="n">
-        <v>98989</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2972,108 +2984,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>130382901</v>
-      </c>
-      <c r="B25" t="n">
-        <v>98989</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Nordansjö naturreservat, Upl</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>604824</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6674944</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54350-2025 artfynd.xlsx
+++ b/artfynd/A 54350-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177129</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117171933</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177137</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177138</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177141</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177143</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177145</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177146</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177148</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177149</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177150</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177151</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177153</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2587,6 +2682,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177154</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2684,6 +2784,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177155</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2781,6 +2886,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177157</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382901</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,8 +3099,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>